--- a/Database/Loplon.xlsx
+++ b/Database/Loplon.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DATTTN_NHOM04_2026\Database\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DFE4870-80E0-430E-84B5-D5C678F12D8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{502AFFD4-9F83-4687-A3AE-3F485C6821E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{29437FEF-AC2B-44F0-9A67-1221192838F4}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="31">
   <si>
     <t>STT</t>
   </si>
@@ -93,6 +93,42 @@
   </si>
   <si>
     <t>DH52300018@student.stu.edu.vn</t>
+  </si>
+  <si>
+    <t>DH52200320</t>
+  </si>
+  <si>
+    <t>Anh</t>
+  </si>
+  <si>
+    <t>D22_TH10</t>
+  </si>
+  <si>
+    <t>DH52200320@student.stu.edu.vn</t>
+  </si>
+  <si>
+    <t>DH52300086</t>
+  </si>
+  <si>
+    <t>D23_TH05</t>
+  </si>
+  <si>
+    <t>DH52300086@student.stu.edu.vn</t>
+  </si>
+  <si>
+    <t>DH52300101</t>
+  </si>
+  <si>
+    <t>Dương Hoàng</t>
+  </si>
+  <si>
+    <t>Ân</t>
+  </si>
+  <si>
+    <t>D23_TH03</t>
+  </si>
+  <si>
+    <t>DH52300101@student.stu.edu.vn</t>
   </si>
 </sst>
 </file>
@@ -477,7 +513,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9469B63F-70E8-4D7D-98A8-2DE8CE955957}">
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="11.5" bestFit="1" customWidth="1"/>
@@ -559,6 +595,66 @@
         <v>18</v>
       </c>
     </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E4" t="s">
+        <v>21</v>
+      </c>
+      <c r="H4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>23</v>
+      </c>
+      <c r="C5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E5" t="s">
+        <v>24</v>
+      </c>
+      <c r="H5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>26</v>
+      </c>
+      <c r="C6" t="s">
+        <v>27</v>
+      </c>
+      <c r="D6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E6" t="s">
+        <v>29</v>
+      </c>
+      <c r="H6" t="s">
+        <v>30</v>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="H2" r:id="rId1" xr:uid="{3F6AA5CE-2B8C-421E-A790-75BCDB0DA393}"/>
